--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-24T14:33:01.184Z</t>
+    <t>2026-07-24T16:37:09.129Z</t>
   </si>
   <si>
     <t>Remarkable template</t>
